--- a/originales/respuestas/2025/01. Calificadas/bucle p2/Empresa De Renovación Y Desarrollo Urbano De Bogotá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p2/Empresa De Renovación Y Desarrollo Urbano De Bogotá.xlsx
@@ -4,19 +4,23 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Hoja1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="p1" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="YzxOSbOqrOHWxEYCtQLaBtNV1KppYQ4mUEu5NNflgYg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="m8shFgyD17hGntlQRSEpG80XcBTTLchygt1thaCaWQ0="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+  <si>
+    <t>Hoja1</t>
+  </si>
   <si>
     <t>Entidad</t>
   </si>
@@ -112,9 +116,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -217,32 +226,35 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -252,6 +264,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -452,6 +468,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
@@ -461,191 +494,191 @@
   </cols>
   <sheetData>
     <row r="1" ht="43.5" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
+      <c r="Q1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
     </row>
     <row r="2" ht="126.75" customHeight="1">
-      <c r="A2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="5">
+      <c r="G2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="6">
         <v>5.0</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="7">
+      <c r="I2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="8">
         <v>3.0</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="7">
+      <c r="K2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="8">
         <v>2.0</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="5">
+      <c r="M2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="6">
         <v>5.0</v>
       </c>
-      <c r="O2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" s="7">
+      <c r="O2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="8">
         <v>3.0</v>
       </c>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="8"/>
-      <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8"/>
-      <c r="AB2" s="8"/>
-      <c r="AC2" s="8"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
     </row>
     <row r="3" ht="126.75" customHeight="1">
-      <c r="A3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="8">
+        <v>4.0</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="8">
+        <v>3.0</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="O3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="7">
+      <c r="P3" s="8">
         <v>4.0</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="8"/>
-      <c r="AB3" s="8"/>
-      <c r="AC3" s="8"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
     </row>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>

--- a/originales/respuestas/2025/01. Calificadas/bucle p2/Empresa De Renovación Y Desarrollo Urbano De Bogotá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p2/Empresa De Renovación Y Desarrollo Urbano De Bogotá.xlsx
@@ -10,17 +10,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="m8shFgyD17hGntlQRSEpG80XcBTTLchygt1thaCaWQ0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="OuICa48JyveFFW8J/um9DZ4PsrkQpGoBp1wYnxooLQY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
-  <si>
-    <t>Hoja1</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>Entidad</t>
   </si>
@@ -116,14 +113,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -226,35 +218,32 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -471,13 +460,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -494,191 +477,191 @@
   </cols>
   <sheetData>
     <row r="1" ht="43.5" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
     </row>
     <row r="2" ht="126.75" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="6">
+      <c r="J2" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="5">
         <v>5.0</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="8">
+      <c r="O2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="7">
         <v>3.0</v>
       </c>
-      <c r="K2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="8">
-        <v>3.0</v>
-      </c>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+      <c r="Z2" s="8"/>
+      <c r="AA2" s="8"/>
+      <c r="AB2" s="8"/>
+      <c r="AC2" s="8"/>
     </row>
     <row r="3" ht="126.75" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="6">
+      <c r="J3" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="5">
         <v>5.0</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="8">
+      <c r="O3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="7">
         <v>4.0</v>
       </c>
-      <c r="K3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="8">
-        <v>3.0</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" s="8">
-        <v>4.0</v>
-      </c>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8"/>
+      <c r="AB3" s="8"/>
+      <c r="AC3" s="8"/>
     </row>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
